--- a/data/trans_orig/P0902-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P0902-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2007</t>
+          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>138077</t>
+          <t>138890</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>183486</t>
+          <t>183896</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>278407</t>
+          <t>277495</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>339721</t>
+          <t>341007</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>427221</t>
+          <t>430422</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>506420</t>
+          <t>510117</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,74%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>848237</t>
+          <t>847827</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>893646</t>
+          <t>892833</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>975392</t>
+          <t>974106</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1036706</t>
+          <t>1037618</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1840415</t>
+          <t>1836718</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1919614</t>
+          <t>1916413</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,66%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67663</t>
+          <t>67811</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>106166</t>
+          <t>103491</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>126502</t>
+          <t>124527</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>170682</t>
+          <t>170993</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>201686</t>
+          <t>201146</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>260657</t>
+          <t>258335</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1587247</t>
+          <t>1589922</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1625750</t>
+          <t>1625602</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1416991</t>
+          <t>1416680</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1461171</t>
+          <t>1463146</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3020429</t>
+          <t>3022751</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3079400</t>
+          <t>3079940</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,87%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14577</t>
+          <t>14416</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34032</t>
+          <t>34852</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27520</t>
+          <t>28245</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54165</t>
+          <t>52060</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48139</t>
+          <t>47151</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79982</t>
+          <t>79997</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>517376</t>
+          <t>516556</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>536831</t>
+          <t>536992</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>422247</t>
+          <t>424352</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>448892</t>
+          <t>448167</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>947838</t>
+          <t>947823</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>979681</t>
+          <t>980669</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,41%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>238988</t>
+          <t>238484</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>302230</t>
+          <t>303784</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>451936</t>
+          <t>452227</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>535285</t>
+          <t>533460</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>713886</t>
+          <t>711231</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>816233</t>
+          <t>815883</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2974313</t>
+          <t>2972759</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3037555</t>
+          <t>3038059</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2843912</t>
+          <t>2845737</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2927261</t>
+          <t>2926970</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5839508</t>
+          <t>5839858</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5941855</t>
+          <t>5944510</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,31%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2012</t>
+          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>197472</t>
+          <t>200901</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>253554</t>
+          <t>257857</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>441104</t>
+          <t>437926</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>511466</t>
+          <t>512355</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>655354</t>
+          <t>658947</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>749858</t>
+          <t>749267</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,4%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>721089</t>
+          <t>716786</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>777171</t>
+          <t>773742</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>826331</t>
+          <t>825442</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>896693</t>
+          <t>899871</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1562582</t>
+          <t>1563173</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1657086</t>
+          <t>1653493</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,5%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>100919</t>
+          <t>102391</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>144555</t>
+          <t>144346</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>171303</t>
+          <t>172548</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>227496</t>
+          <t>227478</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>287060</t>
+          <t>285561</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>355425</t>
+          <t>352069</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1818482</t>
+          <t>1818691</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1862118</t>
+          <t>1860646</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1527330</t>
+          <t>1527348</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1583523</t>
+          <t>1582278</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3362438</t>
+          <t>3365794</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3430803</t>
+          <t>3432302</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,32%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17722</t>
+          <t>18348</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41171</t>
+          <t>42424</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25191</t>
+          <t>24849</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49319</t>
+          <t>48828</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47770</t>
+          <t>48087</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79818</t>
+          <t>83322</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>440010</t>
+          <t>438757</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>463459</t>
+          <t>462833</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>408343</t>
+          <t>408834</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>432471</t>
+          <t>432813</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>859026</t>
+          <t>855522</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>891074</t>
+          <t>890757</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,88%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>336437</t>
+          <t>342387</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>411889</t>
+          <t>417160</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>662424</t>
+          <t>660382</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>761585</t>
+          <t>759563</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1021915</t>
+          <t>1020506</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1147552</t>
+          <t>1143885</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3006972</t>
+          <t>3001701</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3082424</t>
+          <t>3076474</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2788700</t>
+          <t>2790722</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2887861</t>
+          <t>2889903</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5821594</t>
+          <t>5825261</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5947231</t>
+          <t>5948640</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,36%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2016</t>
+          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>132917</t>
+          <t>133434</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>177720</t>
+          <t>177643</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>316197</t>
+          <t>313184</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>379727</t>
+          <t>379704</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>464007</t>
+          <t>466401</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>542660</t>
+          <t>541511</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,96%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>576627</t>
+          <t>576704</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>621430</t>
+          <t>620913</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>614933</t>
+          <t>614956</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>678463</t>
+          <t>681476</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1206347</t>
+          <t>1207496</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1285000</t>
+          <t>1282606</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>73,33%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>109616</t>
+          <t>108296</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>153058</t>
+          <t>155754</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>199416</t>
+          <t>200457</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>259917</t>
+          <t>259932</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>324056</t>
+          <t>323873</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>399212</t>
+          <t>399351</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1923327</t>
+          <t>1920631</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1966769</t>
+          <t>1968089</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1728383</t>
+          <t>1728368</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1788884</t>
+          <t>1787843</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3665473</t>
+          <t>3665334</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3740629</t>
+          <t>3740812</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17075</t>
+          <t>17027</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39614</t>
+          <t>39883</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36034</t>
+          <t>35827</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66048</t>
+          <t>66061</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59189</t>
+          <t>59164</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>99618</t>
+          <t>94298</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>507272</t>
+          <t>507003</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>529811</t>
+          <t>529859</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>483092</t>
+          <t>483079</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>513106</t>
+          <t>513313</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>996409</t>
+          <t>1001729</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1036838</t>
+          <t>1036863</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>277369</t>
+          <t>279454</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>346241</t>
+          <t>348669</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>577812</t>
+          <t>575906</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>668724</t>
+          <t>676220</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>877560</t>
+          <t>877347</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1002585</t>
+          <t>994714</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3031377</t>
+          <t>3028949</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3100249</t>
+          <t>3098164</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2863376</t>
+          <t>2855880</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2954288</t>
+          <t>2956194</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5907133</t>
+          <t>5915004</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6032158</t>
+          <t>6032371</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2023</t>
+          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>124295</t>
+          <t>123284</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>162087</t>
+          <t>161129</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>296885</t>
+          <t>296488</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>339894</t>
+          <t>341407</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>433325</t>
+          <t>434424</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>486414</t>
+          <t>488366</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,46%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>352072</t>
+          <t>353030</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>389864</t>
+          <t>390875</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>76,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>415614</t>
+          <t>414101</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>458623</t>
+          <t>459020</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>783253</t>
+          <t>781301</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>836342</t>
+          <t>835243</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>65,78%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>149039</t>
+          <t>159054</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>260020</t>
+          <t>260048</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>200401</t>
+          <t>209397</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>323877</t>
+          <t>323867</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>397992</t>
+          <t>404614</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>559725</t>
+          <t>565344</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2028143</t>
+          <t>2028115</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2139124</t>
+          <t>2129109</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1912339</t>
+          <t>1912349</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2035815</t>
+          <t>2026819</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3964654</t>
+          <t>3959035</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4126387</t>
+          <t>4119765</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,06%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37129</t>
+          <t>37797</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65437</t>
+          <t>65849</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48033</t>
+          <t>48950</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72845</t>
+          <t>72165</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>91081</t>
+          <t>93495</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>126563</t>
+          <t>128589</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>581186</t>
+          <t>580774</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>609494</t>
+          <t>608826</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>587618</t>
+          <t>588298</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>612430</t>
+          <t>611513</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1180523</t>
+          <t>1178497</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1216005</t>
+          <t>1213591</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,85%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>322593</t>
+          <t>307117</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>460278</t>
+          <t>458928</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>535610</t>
+          <t>550602</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>715984</t>
+          <t>724485</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>929642</t>
+          <t>926296</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1152497</t>
+          <t>1149995</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2988667</t>
+          <t>2990017</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3126352</t>
+          <t>3141828</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2936203</t>
+          <t>2927702</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3116577</t>
+          <t>3101585</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5948635</t>
+          <t>5951137</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6171490</t>
+          <t>6174836</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>86,96%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P0902-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P0902-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>138890</t>
+          <t>138381</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>183896</t>
+          <t>185138</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>277495</t>
+          <t>278852</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>341007</t>
+          <t>339370</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>430422</t>
+          <t>433116</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>510117</t>
+          <t>504669</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,5%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>847827</t>
+          <t>846585</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>892833</t>
+          <t>893342</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>974106</t>
+          <t>975743</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1037618</t>
+          <t>1036261</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1836718</t>
+          <t>1842166</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1916413</t>
+          <t>1913719</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,54%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67811</t>
+          <t>68083</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>103491</t>
+          <t>103333</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>124527</t>
+          <t>123785</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>170993</t>
+          <t>170097</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>201146</t>
+          <t>202826</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>258335</t>
+          <t>259458</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1589922</t>
+          <t>1590080</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1625602</t>
+          <t>1625330</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1416680</t>
+          <t>1417576</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1463146</t>
+          <t>1463888</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3022751</t>
+          <t>3021628</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3079940</t>
+          <t>3078260</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,82%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14416</t>
+          <t>14849</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34852</t>
+          <t>35033</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28245</t>
+          <t>28453</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52060</t>
+          <t>54158</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47151</t>
+          <t>48397</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79997</t>
+          <t>80896</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>516556</t>
+          <t>516375</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>536992</t>
+          <t>536559</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>424352</t>
+          <t>422254</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>448167</t>
+          <t>447959</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>947823</t>
+          <t>946924</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>980669</t>
+          <t>979423</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,29%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>238484</t>
+          <t>239433</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>303784</t>
+          <t>300171</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>452227</t>
+          <t>453785</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>533460</t>
+          <t>535608</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>711231</t>
+          <t>712708</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>815883</t>
+          <t>815514</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,25%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2972759</t>
+          <t>2976372</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3038059</t>
+          <t>3037110</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2845737</t>
+          <t>2843589</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2926970</t>
+          <t>2925412</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5839858</t>
+          <t>5840227</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5944510</t>
+          <t>5943033</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,29%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>200901</t>
+          <t>199203</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>257857</t>
+          <t>258709</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>437926</t>
+          <t>439956</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>512355</t>
+          <t>512141</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>658947</t>
+          <t>654472</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>749267</t>
+          <t>747803</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,34%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>716786</t>
+          <t>715934</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>773742</t>
+          <t>775440</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>825442</t>
+          <t>825656</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>899871</t>
+          <t>897841</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1563173</t>
+          <t>1564637</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1653493</t>
+          <t>1657968</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,7%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>102391</t>
+          <t>95934</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>144346</t>
+          <t>143376</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>172548</t>
+          <t>173943</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>227478</t>
+          <t>228936</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>285561</t>
+          <t>286200</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>352069</t>
+          <t>359360</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1818691</t>
+          <t>1819661</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1860646</t>
+          <t>1867103</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1527348</t>
+          <t>1525890</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1582278</t>
+          <t>1580883</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3365794</t>
+          <t>3358503</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3432302</t>
+          <t>3431663</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,3%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18348</t>
+          <t>18934</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42424</t>
+          <t>42691</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24849</t>
+          <t>24137</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48828</t>
+          <t>48201</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48087</t>
+          <t>47403</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>83322</t>
+          <t>81040</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>438757</t>
+          <t>438490</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>462833</t>
+          <t>462247</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>408834</t>
+          <t>409461</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>432813</t>
+          <t>433525</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>855522</t>
+          <t>857804</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>890757</t>
+          <t>891441</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,95%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>342387</t>
+          <t>340603</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>417160</t>
+          <t>420485</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>660382</t>
+          <t>655879</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>759563</t>
+          <t>753749</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1020506</t>
+          <t>1020231</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1143885</t>
+          <t>1147576</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3001701</t>
+          <t>2998376</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3076474</t>
+          <t>3078258</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2790722</t>
+          <t>2796536</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2889903</t>
+          <t>2894406</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5825261</t>
+          <t>5821570</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5948640</t>
+          <t>5948915</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>133434</t>
+          <t>135882</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>177643</t>
+          <t>176485</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>313184</t>
+          <t>314942</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>379704</t>
+          <t>376906</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>466401</t>
+          <t>461554</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>541511</t>
+          <t>539548</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,85%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>576704</t>
+          <t>577862</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>620913</t>
+          <t>618465</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>614956</t>
+          <t>617754</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>681476</t>
+          <t>679718</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1207496</t>
+          <t>1209459</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1282606</t>
+          <t>1287453</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,61%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>108296</t>
+          <t>110270</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>155754</t>
+          <t>155832</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>200457</t>
+          <t>198750</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>259932</t>
+          <t>259741</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>323873</t>
+          <t>320958</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>399351</t>
+          <t>395617</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1920631</t>
+          <t>1920553</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1968089</t>
+          <t>1966115</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1728368</t>
+          <t>1728559</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1787843</t>
+          <t>1789550</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3665334</t>
+          <t>3669068</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3740812</t>
+          <t>3743727</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,1%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17027</t>
+          <t>17625</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39883</t>
+          <t>40088</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35827</t>
+          <t>35060</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66061</t>
+          <t>66054</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59164</t>
+          <t>57669</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>94298</t>
+          <t>94282</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>507003</t>
+          <t>506798</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>529859</t>
+          <t>529261</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>483079</t>
+          <t>483086</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>513313</t>
+          <t>514080</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1001729</t>
+          <t>1001745</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1036863</t>
+          <t>1038358</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,74%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>279454</t>
+          <t>280465</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>348669</t>
+          <t>351656</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>575906</t>
+          <t>579206</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>676220</t>
+          <t>677295</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>877347</t>
+          <t>880258</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>994714</t>
+          <t>999194</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,46%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3028949</t>
+          <t>3025962</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3098164</t>
+          <t>3097153</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2855880</t>
+          <t>2854805</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2956194</t>
+          <t>2952894</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5915004</t>
+          <t>5910524</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6032371</t>
+          <t>6029460</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,26%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>141189</t>
+          <t>151153</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>123284</t>
+          <t>132507</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>161129</t>
+          <t>170399</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>318190</t>
+          <t>342116</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>296488</t>
+          <t>320542</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>341407</t>
+          <t>365084</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>459379</t>
+          <t>493269</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>434424</t>
+          <t>467956</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>488366</t>
+          <t>525811</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>37,57%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>372970</t>
+          <t>426373</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>353030</t>
+          <t>407127</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>390875</t>
+          <t>445019</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>437318</t>
+          <t>479922</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>414101</t>
+          <t>456954</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>459020</t>
+          <t>501496</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>810288</t>
+          <t>906295</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>781301</t>
+          <t>873753</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>835243</t>
+          <t>931608</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>66,56%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514159</t>
+          <t>577526</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514159</t>
+          <t>577526</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514159</t>
+          <t>577526</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1269667</t>
+          <t>1399564</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1269667</t>
+          <t>1399564</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1269667</t>
+          <t>1399564</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>219265</t>
+          <t>236349</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>159054</t>
+          <t>207191</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>260048</t>
+          <t>266490</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>279654</t>
+          <t>316148</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>209397</t>
+          <t>287821</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>323867</t>
+          <t>345485</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>498919</t>
+          <t>552497</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>404614</t>
+          <t>508786</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>565344</t>
+          <t>595904</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2068898</t>
+          <t>1992034</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2028115</t>
+          <t>1961893</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2129109</t>
+          <t>2021192</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1956562</t>
+          <t>1853555</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1912349</t>
+          <t>1824218</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2026819</t>
+          <t>1881882</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4025460</t>
+          <t>3845590</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3959035</t>
+          <t>3802183</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4119765</t>
+          <t>3889301</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>88,43%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2288163</t>
+          <t>2228383</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2288163</t>
+          <t>2228383</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2288163</t>
+          <t>2228383</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2236216</t>
+          <t>2169703</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2236216</t>
+          <t>2169703</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2236216</t>
+          <t>2169703</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4524379</t>
+          <t>4398087</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4524379</t>
+          <t>4398087</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4524379</t>
+          <t>4398087</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>49050</t>
+          <t>52614</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37797</t>
+          <t>39813</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65849</t>
+          <t>68786</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>60134</t>
+          <t>72098</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48950</t>
+          <t>59407</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72165</t>
+          <t>86422</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>109184</t>
+          <t>124712</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>93495</t>
+          <t>106152</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>128589</t>
+          <t>147654</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>597573</t>
+          <t>658973</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>580774</t>
+          <t>642801</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>608826</t>
+          <t>671774</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>600329</t>
+          <t>662779</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>588298</t>
+          <t>648455</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>611513</t>
+          <t>675470</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1197902</t>
+          <t>1321752</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1178497</t>
+          <t>1298810</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1213591</t>
+          <t>1340312</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,66%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>409505</t>
+          <t>440116</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>307117</t>
+          <t>398040</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>458928</t>
+          <t>479971</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>657978</t>
+          <t>730361</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>550602</t>
+          <t>694108</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>724485</t>
+          <t>769448</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1067483</t>
+          <t>1170478</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>926296</t>
+          <t>1119007</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1149995</t>
+          <t>1228286</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,96%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3039440</t>
+          <t>3077381</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2990017</t>
+          <t>3037526</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3141828</t>
+          <t>3119457</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2994209</t>
+          <t>2996257</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2927702</t>
+          <t>2957170</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3101585</t>
+          <t>3032510</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6033649</t>
+          <t>6073637</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5951137</t>
+          <t>6015829</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6174836</t>
+          <t>6125108</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>84,55%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3448945</t>
+          <t>3517497</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3448945</t>
+          <t>3517497</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3448945</t>
+          <t>3517497</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3652187</t>
+          <t>3726618</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3652187</t>
+          <t>3726618</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3652187</t>
+          <t>3726618</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7101132</t>
+          <t>7244115</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7101132</t>
+          <t>7244115</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7101132</t>
+          <t>7244115</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
